--- a/business_surveys/018_understanding_delivered_duty_paid_ddp--business_surveys.xlsx
+++ b/business_surveys/018_understanding_delivered_duty_paid_ddp--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -926,8 +926,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -955,12 +955,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'faster_clearance'}</t>
+          <t>faster_clearance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Faster Clearance'}</t>
+          <t>Faster Clearance</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'reduced_fees'}</t>
+          <t>reduced_fees</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Reduced Fees'}</t>
+          <t>Reduced Fees</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'improved_tracking'}</t>
+          <t>improved_tracking</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Improved Tracking'}</t>
+          <t>Improved Tracking</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Agree'}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Disagree'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
